--- a/Assets/Data/Dungeon0051.xlsx
+++ b/Assets/Data/Dungeon0051.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8410" activeTab="3"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="3" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="30">
   <si>
     <t>Id</t>
   </si>
@@ -55,22 +55,34 @@
     <t>Mv</t>
   </si>
   <si>
-    <t>Ba</t>
+    <t>Tr:D4</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Tr:D1</t>
   </si>
   <si>
     <t>Mg</t>
-  </si>
-  <si>
-    <t>Tr:D2</t>
-  </si>
-  <si>
-    <t>Dr</t>
   </si>
   <si>
     <t>Dm</t>
   </si>
   <si>
     <t>Ar:D3</t>
+  </si>
+  <si>
+    <t>Ba</t>
+  </si>
+  <si>
+    <t>②</t>
+  </si>
+  <si>
+    <t>①</t>
+  </si>
+  <si>
+    <t>Un</t>
   </si>
   <si>
     <t>PositionX</t>
@@ -105,10 +117,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -128,7 +140,53 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -142,8 +200,53 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -158,47 +261,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -213,58 +276,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -279,7 +291,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -291,49 +411,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -345,55 +429,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -411,31 +447,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -447,19 +471,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -473,45 +485,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -521,27 +494,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -570,6 +526,62 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -578,145 +590,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -739,12 +751,12 @@
     <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
     <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
     <cellStyle name="通貨" xfId="6" builtinId="4"/>
-    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
-    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
-    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
-    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
-    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
-    <cellStyle name="メモ" xfId="12" builtinId="10"/>
+    <cellStyle name="20% - アクセント 4" xfId="7" builtinId="42"/>
+    <cellStyle name="メモ" xfId="8" builtinId="10"/>
+    <cellStyle name="パーセント" xfId="9" builtinId="5"/>
+    <cellStyle name="ハイパーリンク" xfId="10" builtinId="8"/>
+    <cellStyle name="アクセント 2" xfId="11" builtinId="33"/>
+    <cellStyle name="訪問済ハイパーリンク" xfId="12" builtinId="9"/>
     <cellStyle name="良い" xfId="13" builtinId="26"/>
     <cellStyle name="警告文" xfId="14" builtinId="11"/>
     <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
@@ -840,169 +852,185 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>2010</v>
+            <v>1030</v>
           </cell>
           <cell r="E5" t="str">
-            <v>ダンジョンから出る</v>
+            <v>メインイベント再生</v>
           </cell>
         </row>
         <row r="6">
           <cell r="D6">
-            <v>2020</v>
+            <v>2010</v>
           </cell>
           <cell r="E6" t="str">
-            <v>ダンジョン移動</v>
+            <v>ダンジョンから出る</v>
           </cell>
         </row>
         <row r="7">
           <cell r="D7">
-            <v>2021</v>
+            <v>2011</v>
           </cell>
           <cell r="E7" t="str">
-            <v>移動判定なしでダンジョン移動</v>
+            <v>ダンジョンから出る（確認無し）</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>2030</v>
+            <v>2020</v>
           </cell>
           <cell r="E8" t="str">
-            <v>ダンジョンクリア</v>
+            <v>ダンジョン移動</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>3010</v>
+            <v>2021</v>
           </cell>
           <cell r="E9" t="str">
-            <v>アーティファクト取得</v>
+            <v>移動判定なしでダンジョン移動</v>
           </cell>
         </row>
         <row r="10">
           <cell r="D10">
-            <v>3020</v>
+            <v>2030</v>
           </cell>
           <cell r="E10" t="str">
-            <v>アイテム取得</v>
+            <v>ダンジョンクリア</v>
           </cell>
         </row>
         <row r="11">
           <cell r="D11">
-            <v>3030</v>
+            <v>3010</v>
           </cell>
           <cell r="E11" t="str">
-            <v>魔法入手</v>
+            <v>アーティファクト取得</v>
           </cell>
         </row>
         <row r="12">
           <cell r="D12">
-            <v>4010</v>
+            <v>3020</v>
           </cell>
           <cell r="E12" t="str">
-            <v>仲間を増やす</v>
+            <v>アイテム取得</v>
           </cell>
         </row>
         <row r="13">
           <cell r="D13">
-            <v>4011</v>
+            <v>3030</v>
           </cell>
           <cell r="E13" t="str">
-            <v>仲間を外す</v>
+            <v>魔法入手</v>
           </cell>
         </row>
         <row r="14">
           <cell r="D14">
-            <v>4020</v>
+            <v>4010</v>
           </cell>
           <cell r="E14" t="str">
-            <v>選択して仲間を増やす</v>
+            <v>仲間を増やす</v>
           </cell>
         </row>
         <row r="15">
           <cell r="D15">
-            <v>5010</v>
+            <v>4011</v>
           </cell>
           <cell r="E15" t="str">
-            <v>強制戦闘</v>
+            <v>仲間を外す</v>
           </cell>
         </row>
         <row r="16">
           <cell r="D16">
-            <v>5020</v>
+            <v>4020</v>
           </cell>
           <cell r="E16" t="str">
-            <v>強制ボス戦闘</v>
+            <v>選択して仲間を増やす</v>
           </cell>
         </row>
         <row r="17">
           <cell r="D17">
-            <v>6010</v>
+            <v>5010</v>
           </cell>
           <cell r="E17" t="str">
-            <v>指定のイベントマスを消す</v>
+            <v>強制戦闘</v>
           </cell>
         </row>
         <row r="18">
           <cell r="D18">
-            <v>6011</v>
+            <v>5020</v>
           </cell>
           <cell r="E18" t="str">
-            <v>指定のイベントマスを表示する</v>
+            <v>強制ボス戦闘</v>
           </cell>
         </row>
         <row r="19">
           <cell r="D19">
-            <v>6020</v>
+            <v>6010</v>
           </cell>
           <cell r="E19" t="str">
-            <v>同フロアの強制戦闘が終わってたらイベントマスを消す</v>
+            <v>指定のイベントマスを消す</v>
           </cell>
         </row>
         <row r="20">
           <cell r="D20">
-            <v>6030</v>
+            <v>6011</v>
           </cell>
           <cell r="E20" t="str">
-            <v>同フロアの強制戦闘が終わってたらイベントマスを表示する</v>
+            <v>指定のイベントマスを表示する</v>
           </cell>
         </row>
         <row r="21">
           <cell r="D21">
-            <v>7010</v>
+            <v>6020</v>
           </cell>
           <cell r="E21" t="str">
-            <v>ダメージ床</v>
+            <v>同フロアの強制戦闘が終わってたらイベントマスを消す</v>
           </cell>
         </row>
         <row r="22">
           <cell r="D22">
-            <v>7020</v>
+            <v>6030</v>
           </cell>
           <cell r="E22" t="str">
-            <v>怨嗟床</v>
+            <v>同フロアの強制戦闘が終わってたらイベントマスを表示する</v>
           </cell>
         </row>
         <row r="23">
           <cell r="D23">
-            <v>7021</v>
+            <v>7010</v>
           </cell>
           <cell r="E23" t="str">
-            <v>怨嗟床解除</v>
+            <v>ダメージ床</v>
           </cell>
         </row>
         <row r="24">
           <cell r="D24">
-            <v>8010</v>
+            <v>7020</v>
           </cell>
           <cell r="E24" t="str">
-            <v>指定リージョンを開示する</v>
+            <v>怨嗟床</v>
           </cell>
         </row>
         <row r="25">
           <cell r="D25">
+            <v>7021</v>
+          </cell>
+          <cell r="E25" t="str">
+            <v>怨嗟床解除</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="D26">
+            <v>8010</v>
+          </cell>
+          <cell r="E26" t="str">
+            <v>指定リージョンを開示する</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="D27">
             <v>9010</v>
           </cell>
-          <cell r="E25" t="str">
+          <cell r="E27" t="str">
             <v>イベント終了明示</v>
           </cell>
         </row>
@@ -1339,16 +1367,16 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H2">
         <v>2</v>
@@ -1460,19 +1488,19 @@
         <v>8</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>8</v>
@@ -1481,13 +1509,13 @@
         <v>8</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M2" s="2" t="s">
         <v>8</v>
@@ -1498,15 +1526,9 @@
       <c r="O2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
       <c r="S2" s="2"/>
       <c r="T2" s="2"/>
       <c r="U2" s="2"/>
@@ -1539,19 +1561,19 @@
         <v>8</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="G3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>8</v>
@@ -1560,13 +1582,13 @@
         <v>8</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>8</v>
@@ -1577,15 +1599,9 @@
       <c r="O3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
       <c r="S3" s="2"/>
       <c r="T3" s="2"/>
       <c r="U3" s="2"/>
@@ -1618,17 +1634,17 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="F4" s="2"/>
       <c r="G4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>8</v>
@@ -1637,13 +1653,11 @@
         <v>8</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="K4" s="2"/>
       <c r="L4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>8</v>
@@ -1654,15 +1668,9 @@
       <c r="O4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
       <c r="U4" s="2"/>
@@ -1692,54 +1700,50 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
       <c r="S5" s="2"/>
       <c r="T5" s="2"/>
       <c r="U5" s="2"/>
@@ -1769,54 +1773,34 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>9</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
       <c r="H6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>9</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
       <c r="L6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>9</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
       <c r="O6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="P6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
       <c r="S6" s="2"/>
       <c r="T6" s="2"/>
       <c r="U6" s="2"/>
@@ -1846,35 +1830,48 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
+      <c r="D7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
+      <c r="L7" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="M7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="O7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
       <c r="S7" s="2"/>
       <c r="T7" s="2"/>
       <c r="U7" s="2"/>
@@ -1907,50 +1904,45 @@
         <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="K8" s="2"/>
       <c r="L8" s="2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>9</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
       <c r="S8" s="2"/>
       <c r="T8" s="2"/>
       <c r="U8" s="2"/>
@@ -1983,13 +1975,13 @@
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>8</v>
@@ -1998,28 +1990,30 @@
         <v>8</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="P9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R9" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
       <c r="S9" s="2"/>
       <c r="T9" s="2"/>
       <c r="U9" s="2"/>
@@ -2049,30 +2043,36 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
+      <c r="I10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
+      <c r="L10" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="M10" s="2" t="s">
         <v>9</v>
       </c>
@@ -2082,15 +2082,9 @@
       <c r="O10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="P10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
       <c r="S10" s="2"/>
       <c r="T10" s="2"/>
       <c r="U10" s="2"/>
@@ -2122,48 +2116,32 @@
       <c r="B11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
       <c r="E11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>9</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
       <c r="I11" s="2"/>
-      <c r="J11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" t="s">
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="M11" t="s">
         <v>15</v>
       </c>
+      <c r="N11" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="O11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R11" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
       <c r="S11" s="2"/>
       <c r="T11" s="2"/>
       <c r="U11" s="2"/>
@@ -2195,18 +2173,32 @@
       <c r="B12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="J12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>9</v>
@@ -2220,15 +2212,9 @@
       <c r="O12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="P12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R12" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
       <c r="U12" s="2"/>
@@ -2258,35 +2244,33 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="D13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="F13" s="2"/>
       <c r="G13" s="2" t="s">
         <v>9</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K13" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="K13" s="2"/>
       <c r="L13" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M13" s="2" t="s">
         <v>8</v>
@@ -2297,15 +2281,9 @@
       <c r="O13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R13" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
       <c r="S13" s="2"/>
       <c r="T13" s="2"/>
       <c r="U13" s="2"/>
@@ -2335,22 +2313,22 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="G14" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>8</v>
@@ -2359,13 +2337,13 @@
         <v>8</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M14" s="2" t="s">
         <v>8</v>
@@ -2376,15 +2354,9 @@
       <c r="O14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R14" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
       <c r="U14" s="2"/>
@@ -2414,22 +2386,22 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>8</v>
@@ -2438,13 +2410,13 @@
         <v>8</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M15" s="2" t="s">
         <v>8</v>
@@ -2455,15 +2427,9 @@
       <c r="O15" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R15" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
       <c r="S15" s="2"/>
       <c r="T15" s="2"/>
       <c r="U15" s="2"/>
@@ -3653,19 +3619,19 @@
         <v>8</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>8</v>
@@ -3674,13 +3640,13 @@
         <v>8</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M2" s="2" t="s">
         <v>8</v>
@@ -3691,15 +3657,9 @@
       <c r="O2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
       <c r="S2" s="2"/>
       <c r="T2" s="2"/>
       <c r="U2" s="2"/>
@@ -3732,19 +3692,19 @@
         <v>8</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="G3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>8</v>
@@ -3753,13 +3713,13 @@
         <v>8</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>8</v>
@@ -3770,15 +3730,9 @@
       <c r="O3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
       <c r="S3" s="2"/>
       <c r="T3" s="2"/>
       <c r="U3" s="2"/>
@@ -3811,17 +3765,17 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="F4" s="2"/>
       <c r="G4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>8</v>
@@ -3830,13 +3784,11 @@
         <v>8</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="K4" s="2"/>
       <c r="L4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>8</v>
@@ -3847,15 +3799,9 @@
       <c r="O4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
       <c r="U4" s="2"/>
@@ -3885,54 +3831,50 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
       <c r="S5" s="2"/>
       <c r="T5" s="2"/>
       <c r="U5" s="2"/>
@@ -3962,54 +3904,38 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>9</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
       <c r="H6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>9</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
       <c r="L6" s="2" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="P6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
       <c r="S6" s="2"/>
       <c r="T6" s="2"/>
       <c r="U6" s="2"/>
@@ -4039,35 +3965,48 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
+      <c r="D7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
+      <c r="L7" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="M7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="O7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
       <c r="S7" s="2"/>
       <c r="T7" s="2"/>
       <c r="U7" s="2"/>
@@ -4100,50 +4039,45 @@
         <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="K8" s="2"/>
       <c r="L8" s="2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>9</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
       <c r="S8" s="2"/>
       <c r="T8" s="2"/>
       <c r="U8" s="2"/>
@@ -4176,13 +4110,13 @@
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>8</v>
@@ -4191,28 +4125,30 @@
         <v>8</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="P9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R9" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
       <c r="S9" s="2"/>
       <c r="T9" s="2"/>
       <c r="U9" s="2"/>
@@ -4242,30 +4178,36 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
+      <c r="I10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
+      <c r="L10" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="M10" s="2" t="s">
         <v>9</v>
       </c>
@@ -4275,15 +4217,9 @@
       <c r="O10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="P10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
       <c r="S10" s="2"/>
       <c r="T10" s="2"/>
       <c r="U10" s="2"/>
@@ -4316,47 +4252,35 @@
         <v>9</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>9</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
       <c r="I11" s="2"/>
-      <c r="J11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" t="s">
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="M11" t="s">
         <v>15</v>
       </c>
+      <c r="N11" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="O11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R11" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
       <c r="S11" s="2"/>
       <c r="T11" s="2"/>
       <c r="U11" s="2"/>
@@ -4388,18 +4312,32 @@
       <c r="B12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="J12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>9</v>
@@ -4413,15 +4351,9 @@
       <c r="O12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="P12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R12" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
       <c r="U12" s="2"/>
@@ -4451,35 +4383,33 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="D13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="F13" s="2"/>
       <c r="G13" s="2" t="s">
         <v>9</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K13" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="K13" s="2"/>
       <c r="L13" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M13" s="2" t="s">
         <v>8</v>
@@ -4490,15 +4420,9 @@
       <c r="O13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R13" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
       <c r="S13" s="2"/>
       <c r="T13" s="2"/>
       <c r="U13" s="2"/>
@@ -4528,22 +4452,22 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="G14" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>8</v>
@@ -4552,13 +4476,13 @@
         <v>8</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M14" s="2" t="s">
         <v>8</v>
@@ -4569,15 +4493,9 @@
       <c r="O14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R14" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
       <c r="U14" s="2"/>
@@ -4607,22 +4525,22 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>8</v>
@@ -4631,13 +4549,13 @@
         <v>8</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M15" s="2" t="s">
         <v>8</v>
@@ -5749,7 +5667,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="7" max="7" width="24.6363636363636" customWidth="1"/>
@@ -5760,34 +5678,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -5795,7 +5713,7 @@
         <v>51</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C2">
         <v>12</v>
@@ -5814,10 +5732,10 @@
         <v>50</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K2" t="b">
         <v>0</v>
@@ -5828,7 +5746,7 @@
         <v>51</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -5847,10 +5765,10 @@
         <v>52</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K3" t="b">
         <v>0</v>
@@ -5861,10 +5779,10 @@
         <v>51</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C4">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D4">
         <v>3010</v>
@@ -5877,7 +5795,7 @@
         <v>アイテム取得</v>
       </c>
       <c r="H4">
-        <v>1200</v>
+        <v>4020</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5894,23 +5812,23 @@
         <v>51</v>
       </c>
       <c r="B5">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D5">
         <v>3010</v>
       </c>
       <c r="F5">
-        <v>3010</v>
+        <v>3020</v>
       </c>
       <c r="G5" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F5,[1]Define!D:D))</f>
-        <v>アーティファクト取得</v>
+        <v>アイテム取得</v>
       </c>
       <c r="H5">
-        <v>2050</v>
+        <v>4020</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5927,23 +5845,23 @@
         <v>51</v>
       </c>
       <c r="B6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D6">
         <v>3010</v>
       </c>
       <c r="F6">
-        <v>1010</v>
+        <v>3010</v>
       </c>
       <c r="G6" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F6,[1]Define!D:D))</f>
-        <v>Adv再生</v>
+        <v>アーティファクト取得</v>
       </c>
       <c r="H6">
-        <v>140</v>
+        <v>2050</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5960,23 +5878,23 @@
         <v>51</v>
       </c>
       <c r="B7">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D7">
         <v>3010</v>
       </c>
       <c r="F7">
-        <v>6010</v>
+        <v>1010</v>
       </c>
       <c r="G7" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F7,[1]Define!D:D))</f>
-        <v>指定のイベントマスを消す</v>
+        <v>Adv再生</v>
       </c>
       <c r="H7">
-        <v>106</v>
+        <v>140</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5993,22 +5911,26 @@
         <v>51</v>
       </c>
       <c r="B8">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D8">
         <v>3010</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>1020</v>
+      </c>
+      <c r="G8" t="str">
+        <f>INDEX([1]Define!E:E,MATCH(F8,[1]Define!D:D))</f>
+        <v>エンフェリアイベント再生</v>
       </c>
       <c r="H8">
-        <v>106</v>
+        <v>4</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -6022,26 +5944,26 @@
         <v>51</v>
       </c>
       <c r="B9">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D9">
         <v>3010</v>
       </c>
       <c r="F9">
-        <v>1020</v>
+        <v>9010</v>
       </c>
       <c r="G9" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F9,[1]Define!D:D))</f>
-        <v>エンフェリアイベント再生</v>
+        <v>イベント終了明示</v>
       </c>
       <c r="H9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -6055,23 +5977,23 @@
         <v>51</v>
       </c>
       <c r="B10">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C10">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D10">
         <v>3010</v>
       </c>
       <c r="F10">
-        <v>9010</v>
+        <v>7010</v>
       </c>
       <c r="G10" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F10,[1]Define!D:D))</f>
-        <v>イベント終了明示</v>
+        <v>ダメージ床</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -6080,7 +6002,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -6088,32 +6010,32 @@
         <v>51</v>
       </c>
       <c r="B11">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C11">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D11">
         <v>3010</v>
       </c>
       <c r="F11">
-        <v>7010</v>
+        <v>5010</v>
       </c>
       <c r="G11" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F11,[1]Define!D:D))</f>
-        <v>ダメージ床</v>
+        <v>強制戦闘</v>
       </c>
       <c r="H11">
-        <v>20</v>
+        <v>-1</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>40020</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -6121,32 +6043,197 @@
         <v>51</v>
       </c>
       <c r="B12">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C12">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D12">
         <v>3010</v>
       </c>
       <c r="F12">
-        <v>5010</v>
+        <v>1010</v>
       </c>
       <c r="G12" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F12,[1]Define!D:D))</f>
-        <v>強制戦闘</v>
+        <v>Adv再生</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>1070</v>
       </c>
       <c r="I12">
-        <v>40020</v>
+        <v>0</v>
       </c>
       <c r="J12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K12" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13">
+        <v>51</v>
+      </c>
+      <c r="B13">
+        <v>9</v>
+      </c>
+      <c r="C13">
+        <v>10</v>
+      </c>
+      <c r="D13">
+        <v>3010</v>
+      </c>
+      <c r="F13">
+        <v>6010</v>
+      </c>
+      <c r="G13" t="str">
+        <f>INDEX([1]Define!E:E,MATCH(F13,[1]Define!D:D))</f>
+        <v>指定のイベントマスを消す</v>
+      </c>
+      <c r="H13">
+        <v>912</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14">
+        <v>51</v>
+      </c>
+      <c r="B14">
+        <v>9</v>
+      </c>
+      <c r="C14">
+        <v>12</v>
+      </c>
+      <c r="D14">
+        <v>3010</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14" t="str">
+        <f>INDEX([1]Define!E:E,MATCH(F14,[1]Define!D:D))</f>
+        <v>なし</v>
+      </c>
+      <c r="H14">
+        <v>912</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15">
+        <v>51</v>
+      </c>
+      <c r="B15">
+        <v>9</v>
+      </c>
+      <c r="C15">
+        <v>10</v>
+      </c>
+      <c r="D15">
+        <v>3010</v>
+      </c>
+      <c r="F15">
+        <v>5010</v>
+      </c>
+      <c r="G15" t="str">
+        <f>INDEX([1]Define!E:E,MATCH(F15,[1]Define!D:D))</f>
+        <v>強制戦闘</v>
+      </c>
+      <c r="H15">
+        <v>-1</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16">
+        <v>51</v>
+      </c>
+      <c r="B16">
+        <v>3</v>
+      </c>
+      <c r="C16">
+        <v>9</v>
+      </c>
+      <c r="D16">
+        <v>3010</v>
+      </c>
+      <c r="F16">
+        <v>8010</v>
+      </c>
+      <c r="G16" t="str">
+        <f>INDEX([1]Define!E:E,MATCH(F16,[1]Define!D:D))</f>
+        <v>指定リージョンを開示する</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17">
+        <v>51</v>
+      </c>
+      <c r="B17">
+        <v>10</v>
+      </c>
+      <c r="C17">
+        <v>4</v>
+      </c>
+      <c r="D17">
+        <v>3010</v>
+      </c>
+      <c r="F17">
+        <v>8010</v>
+      </c>
+      <c r="G17" t="str">
+        <f>INDEX([1]Define!E:E,MATCH(F17,[1]Define!D:D))</f>
+        <v>指定リージョンを開示する</v>
+      </c>
+      <c r="H17">
+        <v>2</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Dungeon0051.xlsx
+++ b/Assets/Data/Dungeon0051.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="3"/>
+    <workbookView windowWidth="18650" windowHeight="8390"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="3" r:id="rId1"/>
@@ -119,8 +119,8 @@
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -138,73 +138,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -217,7 +154,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -239,14 +184,46 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -261,22 +238,45 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -291,7 +291,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -303,73 +447,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -381,97 +471,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -485,11 +485,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -504,16 +510,55 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -537,51 +582,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -590,145 +590,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -5795,7 +5795,7 @@
         <v>アイテム取得</v>
       </c>
       <c r="H4">
-        <v>4020</v>
+        <v>4310</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5828,7 +5828,7 @@
         <v>アイテム取得</v>
       </c>
       <c r="H5">
-        <v>4020</v>
+        <v>4030</v>
       </c>
       <c r="I5">
         <v>0</v>

--- a/Assets/Data/Dungeon0051.xlsx
+++ b/Assets/Data/Dungeon0051.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="3" r:id="rId1"/>
@@ -139,39 +139,47 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -180,6 +188,21 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -198,9 +221,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -208,59 +246,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -274,9 +268,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -291,13 +291,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -315,7 +381,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -327,7 +423,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -339,139 +471,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,6 +482,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -509,21 +524,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -542,23 +542,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -566,8 +566,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -590,7 +590,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -599,136 +599,136 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -808,9 +808,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Stages"/>
-      <sheetName val="StageEvents"/>
       <sheetName val="StageEnemyRates"/>
-      <sheetName val="Tutorials"/>
       <sheetName val="TextData"/>
       <sheetName val="Define"/>
     </sheetNames>
@@ -818,9 +816,7 @@
       <sheetData sheetId="0"/>
       <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5">
+      <sheetData sheetId="3">
         <row r="1">
           <cell r="D1" t="str">
             <v>Type</v>

--- a/Assets/Data/Dungeon0051.xlsx
+++ b/Assets/Data/Dungeon0051.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="32">
   <si>
     <t>Id</t>
   </si>
@@ -61,7 +61,7 @@
     <t>No</t>
   </si>
   <si>
-    <t>Tr:D1</t>
+    <t>Tr:D3</t>
   </si>
   <si>
     <t>Mg</t>
@@ -70,16 +70,22 @@
     <t>Dm</t>
   </si>
   <si>
-    <t>Ar:D3</t>
+    <t>Ar:D1</t>
   </si>
   <si>
     <t>Ba</t>
+  </si>
+  <si>
+    <t>Tr:D1</t>
   </si>
   <si>
     <t>②</t>
   </si>
   <si>
     <t>①</t>
+  </si>
+  <si>
+    <t>Ar:D3</t>
   </si>
   <si>
     <t>Un</t>
@@ -138,6 +144,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -147,15 +161,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -169,84 +182,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -262,6 +198,35 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -269,14 +234,55 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -291,7 +297,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -303,7 +315,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -315,19 +381,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -339,25 +411,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -369,85 +465,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -459,19 +477,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,21 +488,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -515,35 +506,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -574,6 +547,39 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -590,7 +596,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -599,136 +605,136 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3903,7 +3909,7 @@
         <v>9</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
@@ -3918,13 +3924,13 @@
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>9</v>
@@ -4248,13 +4254,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
@@ -4269,7 +4275,7 @@
         <v>15</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>9</v>
@@ -4475,7 +4481,7 @@
         <v>9</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>9</v>
@@ -5674,34 +5680,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:11">
